--- a/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G05-G08.xlsx
+++ b/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Ningún tema antes de 10.° trabaja la gravedad como causa de las órbitas, y la necesitan la formación del sistema solar, la evolución estelar y las mareas. Se introduce de forma cualitativa. Se paga con la fusión 9.</t>
+          <t>Ningún tema antes de 10.° trabaja la gravedad como causa de las órbitas, y la necesitan la formación del sistema solar, la evolución estelar y las mareas. Se introduce de forma cualitativa. Se paga con la fusión 11.</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,20 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>G05-CIE-U5-5.9</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F5" s="3" t="n">
         <v>6</v>
       </c>
@@ -712,27 +718,27 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>7.6. Explicación de las fases de la Luna, los eclipses y las mareas a partir de los movimientos de la Tierra y la Luna.</t>
+          <t>7.6. Indagación sobre el campo magnético de la Tierra.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Usa un modelo Sol-Tierra-Luna para predecir la fase lunar y el tipo de eclipse, y relaciona la posición de la Luna con las mareas de una tabla de mareas de La Libertad o Acajutla.</t>
+          <t>Usa una brújula y un imán para mostrar que la Tierra se comporta como un gran imán y explica cómo el campo magnético protege al planeta del viento solar.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Mareas, Fases de la Luna, Eclipses solares y lunares</t>
+          <t>Campo magnético terrestre, Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>T8_27-E4.1 Fenómenos observables por los movimientos de la Tierra y la Luna (reforzar: 0 temas, sin cobertura); CO 4, UY 5 (Mareas); prerrequisito: Gravedad y órbitas (acción 1)</t>
+          <t>prerrequisito: Imanes y polos magnéticos (6.°, Física G06 3.8 y 3.9) de Campo magnético terrestre (5.°), brecha 1, confianza alta; reasignación v2: el tema pasa a Ciencias de la Tierra y del Espacio</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>El objetivo E4.1 no tiene temas en el ciclo, y las mareas llegan en 9.° cuando Colombia y Uruguay las enseñan en 4.° y 5.°. Va después de la gravedad. Se paga con la fusión 10.</t>
+          <t>Hoy se enseña en 5.°, antes de los imanes de 6.°. Viaja con la unidad de espacio y queda después de la unidad de Electricidad y magnetismo de 6.° y de la formación de la Tierra.</t>
         </is>
       </c>
     </row>
@@ -742,51 +748,45 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>G05-CIE-U5-5.2, G05-CIE-U5-5.4, G05-CIE-U5-5.1, G05-CIE-U5-5.7</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7. La Tierra en el universo</t>
+          <t>7. La Tierra en el universo (después de 7.6)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7.7. Visualización de las escalas astronómicas de tiempo y distancia. | 7.8. Caracterización de tipos de galaxias: tamaño y formas. | 7.9. Exploración sobre la hipótesis del Big Bang. | 7.10. Exposición sobre misiones de exploración del sistema solar.</t>
+          <t>7.7. Explicación de las fases de la Luna, los eclipses y las mareas a partir de los movimientos de la Tierra y la Luna.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Construye un modelo a escala de distancias del sistema solar y de la galaxia y explica qué es un año luz. | Clasifica imágenes de galaxias en espirales, elípticas e irregulares y ubica la Vía Láctea entre ellas. | Describe en una línea de tiempo las evidencias de que el universo se expande desde un origen común. | Presenta una misión espacial: su objetivo, los instrumentos que llevó y lo que descubrió.</t>
+          <t>Usa un modelo Sol-Tierra-Luna para predecir la fase lunar y el tipo de eclipse, y relaciona la posición de la Luna con las mareas de una tabla de mareas de La Libertad o Acajutla.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo, Origen del universo: el Big Bang, Exploración espacial</t>
+          <t>Mareas, Fases de la Luna, Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>equilibrio: 6.° tiene 0 temas de la asignatura y 5.° concentra 27 de 60 (45 %) (temas_por_grado); prerrequisito: Gravedad y órbitas de Exploración espacial (acción 1)</t>
+          <t>T8_27-E4.1 Fenómenos observables por los movimientos de la Tierra y la Luna (reforzar: 0 temas, sin cobertura); AU 6, CO 4.5, UY 5 (Mareas); prerrequisito: Gravedad y órbitas (acción 1)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>No tienen bloqueos en 5.° ni 6.°. Completan en 6.° la unidad de espacio, de lo cercano a lo lejano (estrellas, galaxias, universo), y dejan 5.° centrado en la geología y el suelo.</t>
+          <t>El objetivo E4.1 no tiene temas en el ciclo, y las mareas llegan en 9.°; Australia las enseña en 6.°, y Colombia y Uruguay antes. Va después de la gravedad. Se paga con la fusión 12.</t>
         </is>
       </c>
     </row>
@@ -801,46 +801,46 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>G07-CIE-U5-5.1</t>
+          <t>G05-CIE-U5-5.2, G05-CIE-U5-5.4, G05-CIE-U5-5.1, G05-CIE-U5-5.7</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2. Calor y temperatura. (después de 2.4, cambios de fase)</t>
+          <t>7. La Tierra en el universo</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2.8. Indagación de las etapas del ciclo del agua y de cómo lo modifican las actividades humanas.</t>
+          <t>7.8. Visualización de las escalas astronómicas de tiempo y distancia. | 7.9. Caracterización de tipos de galaxias: tamaño y formas. | 7.10. Exploración sobre la hipótesis del Big Bang. | 7.11. Exposición sobre misiones de exploración del sistema solar.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Representa en un modelo la evaporación, la condensación, la precipitación, la infiltración y la escorrentía como cambios de fase y señala una actividad de su comunidad que altera alguna etapa.</t>
+          <t>Construye un modelo a escala de distancias del sistema solar y de la galaxia y explica qué es un año luz. | Clasifica imágenes de galaxias en espirales, elípticas e irregulares y ubica la Vía Láctea entre ellas. | Describe en una línea de tiempo las evidencias de que el universo se expande desde un origen común. | Presenta una misión espacial: su objetivo, los instrumentos que llevó y lo que descubrió.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Ciclo del agua, Impacto de las actividades humanas en los recursos</t>
+          <t>Galaxias y escala del universo, Origen del universo: el Big Bang, Exploración espacial</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>SG 5, UY 3 (Ciclo del agua); el archivo no indica bloqueos; prerrequisito en el grafo: Cambios de estado (Física, 6.°: G06 2.4), confianza alta; T8_27-E2.2 El ciclo del agua</t>
+          <t>equilibrio: 6.° tiene 0 temas de la asignatura y 5.° concentra 29 de 64 (45 %) (temas_por_grado); prerrequisito: Gravedad y órbitas de Exploración espacial (acción 1)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Singapur y Uruguay lo enseñan en 5.° y 3.°; El Salvador, en 7.°. Va a 6.°, no a 5.°, para seguir a los cambios de fase de Física (2.4). El ciclo urbano sigue en 7.° (5.2).</t>
+          <t>No tienen bloqueos en 5.° ni 6.°. Completan en 6.° la unidad de espacio, de lo cercano a lo lejano (estrellas, galaxias, universo), y dejan 5.° centrado en la geología y el suelo.</t>
         </is>
       </c>
     </row>
@@ -850,45 +850,51 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>G07-CIE-U5-5.1</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="F8" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5. Recurso hídrico (después de 5.11)</t>
+          <t>6. Ciencias de la Tierra. (antes de 6.14 y 6.15)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5.19. Explicación del calentamiento desigual de la Tierra y de su efecto en los vientos y las corrientes oceánicas superficiales.</t>
+          <t>6.22. Indagación de las etapas del ciclo del agua y de cómo lo modifican las actividades humanas.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Explica con un mapa de vientos y corrientes por qué el ecuador recibe más energía solar que los polos y cómo esa diferencia mueve el aire y el agua superficial del océano.</t>
+          <t>Representa en un modelo la evaporación, la condensación, la precipitación, la infiltración y la escorrentía como cambios de estado del agua y señala una actividad de su comunidad que altera alguna etapa.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica, Corrientes oceánicas superficiales y profundas, Interacción océano-atmósfera</t>
+          <t>Ciclo del agua, Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>CO 4, UY 5 (Corrientes oceánicas superficiales y profundas); prerrequisito: Calentamiento desigual de la Tierra y circulación atmosférica (9.°), bloqueo de Corrientes oceánicas</t>
+          <t>ENG 2, AU 3, UY 3, SG 5 (Ciclo del agua); sin bloqueos; T8_27-E2.2 El ciclo del agua; prerrequisito: cambios de estado del agua (G02 1.8)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Las corrientes y su bloqueo llegan en 9.°. Un tema en 7.° introduce ambos, después de las capas de la atmósfera y antes de los ciclones, que también lo necesitan. Se paga con la fusión 8.</t>
+          <t>Cuatro países, tres de alto desempeño, lo enseñan entre 2.° y 5.°; El Salvador, en 7.°. Sin bloqueos, pasa a 5.° antes del suelo y la erosión. El ciclo urbano sigue en 7.° (5.2).</t>
         </is>
       </c>
     </row>
@@ -898,51 +904,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>G07-CIE-U5-5.14, G07-CIE-U5-5.16</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5. Recurso hídrico</t>
+          <t>5. Recurso hídrico (después de 5.11)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>5.14. Registro y análisis de parámetros meteorológicos con aplicaciones y gráficos.</t>
+          <t>5.19. Explicación del calentamiento desigual de la Tierra y de su efecto en los vientos y las corrientes oceánicas superficiales.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Registra durante una semana temperatura, humedad y precipitación con una aplicación y describe en un gráfico las tendencias observadas.</t>
+          <t>Explica con un mapa de vientos y corrientes por qué el ecuador recibe más energía solar que los polos y cómo esa diferencia mueve el aire y el agua superficial del océano.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica, Corrientes oceánicas superficiales y profundas, Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Tiempo atmosférico y sus variables (también 5.15 y 5.18)</t>
+          <t>CO 4, UY 5 (Corrientes oceánicas superficiales y profundas); prerrequisito: Calentamiento desigual de la Tierra y circulación atmosférica (9.°), bloqueo de Corrientes oceánicas</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>La malla dedica cuatro temas a los parámetros meteorológicos. Registrar los datos y analizar su gráfico son partes de la misma tarea. Libera el tema de la acción 7.</t>
+          <t>Las corrientes y su bloqueo llegan en 9.°. Un tema en 7.° introduce ambos, después de las capas de la atmósfera y antes de los ciclones, que también lo necesitan. Se paga con la fusión 10.</t>
         </is>
       </c>
     </row>
@@ -952,51 +952,51 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G07-CIE-U6-6.7, G07-CIE-U6-6.9</t>
+          <t>G07-CIE-U5-5.15</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6. Ambiente y energía</t>
+          <t>8. El tiempo atmosférico</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6.7. Comparación de los procesos de aprovechamiento de las energías renovables y no renovables.</t>
+          <t>8.1. Construcción y uso de instrumentos para medir parámetros meteorológicos y comparación con el equipo de las estaciones del país.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Compara en un cuadro dos fuentes renovables y dos no renovables según su proceso, su disponibilidad y su impacto ambiental.</t>
+          <t>Construye un pluviómetro o un anemómetro, lo calibra con datos de una estación oficial y explica qué mide cada instrumento de una estación meteorológica.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables, Recursos naturales renovables y no renovables</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Fuentes de energía renovables y no renovables (también 6.2, 6.3, 6.4 y 6.8)</t>
+          <t>AU 2, ENG 2, CO 8.5 (Tiempo atmosférico y sus variables); prerrequisito: Temperatura y escalas termométricas (6.°), bloqueo: impide llegar a 5.°; T8_27-E5.1 Equipo usado en investigaciones de ciencias de la Tierra (reforzar: 0 temas, sin cobertura)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Seis temas de la unidad trabajan las fuentes de energía. Reconocer los procesos renovables y compararlos con los no renovables se unen en un tema. Libera el tema de la acción 1.</t>
+          <t>Inglaterra y Australia trabajan el tiempo atmosférico desde 2.°. Su bloqueo, la temperatura, está en 6.°, así que va a 6.° y no a 5.°. Se reformula para cubrir el objetivo E5.1.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G07-CIE-U6-6.19, G07-CIE-U6-6.20</t>
+          <t>G07-CIE-U5-5.14, G07-CIE-U5-5.16</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1021,36 +1021,36 @@
         <v>7</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>6. Ambiente y energía</t>
+          <t>8. El tiempo atmosférico (después de 8.1)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>6.19. Indagación del concepto de sostenibilidad y de las prácticas que la promueven.</t>
+          <t>8.2. Registro y análisis de parámetros meteorológicos con aplicaciones y gráficos.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Explica qué es la sostenibilidad y propone tres prácticas para su escuela o comunidad, con el recurso que protege cada una.</t>
+          <t>Registra durante una semana temperatura, humedad y precipitación con sus instrumentos o una aplicación y describe en un gráfico las tendencias observadas.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Conservación de recursos, residuos y sostenibilidad</t>
+          <t>fusión: ambos temas trabajan Tiempo atmosférico y sus variables (también 5.15 y 5.18); AU 2, ENG 2, CO 8.5 (Tiempo atmosférico y sus variables); prerrequisito: Temperatura y escalas termométricas (6.°)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>El concepto y sus prácticas se enseñan en dos temas seguidos. Unidos ganan sentido aplicado. Libera el tema de la acción 4.</t>
+          <t>Registrar los datos y analizar su gráfico son una misma tarea. Unidos pasan a 6.° con el tema 5.15, tras las escalas de temperatura (G06 2.3). La fusión libera el tema de la acción 8.</t>
         </is>
       </c>
     </row>
@@ -1060,51 +1060,51 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G05-CIE-U6-6.6</t>
+          <t>G07-CIE-U6-6.7, G07-CIE-U6-6.9</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6. Ciencias de la Tierra.</t>
+          <t>6. Ambiente y energía</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6.6. Modelación de la deriva continental y de las corrientes de convección del manto que la impulsan.</t>
+          <t>6.7. Comparación de los procesos de aprovechamiento de las energías renovables y no renovables.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Reproduce con agua o aceite caliente y piezas flotantes cómo la convección mueve las placas y lo relaciona con la deriva de los continentes.</t>
+          <t>Compara en un cuadro dos fuentes renovables y dos no renovables según su proceso, su disponibilidad y su impacto ambiental.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico, Convección del manto y energía interna de la Tierra</t>
+          <t>Fuentes de energía renovables y no renovables, Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Convección del manto y energía interna de la Tierra (primer grado SV: nunca) de Tectónica de placas (5.°), confianza alta</t>
+          <t>fusión: ambos temas trabajan Fuentes de energía renovables y no renovables (también 6.2, 6.3, 6.4 y 6.8)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>La tectónica de placas (6.7 y 6.8) se enseña sin explicar qué mueve las placas. Se reformula el tema anterior para introducir la convección del manto sin gastar presupuesto.</t>
+          <t>Seis temas de la unidad trabajan las fuentes de energía. Reconocer los procesos renovables y compararlos con los no renovables se unen en un tema. Libera el tema de la acción 1.</t>
         </is>
       </c>
     </row>
@@ -1114,51 +1114,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>G05-CIE-U6-6.9</t>
+          <t>G07-CIE-U6-6.19, G07-CIE-U6-6.20</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>6. Ciencias de la Tierra.</t>
+          <t>6. Ambiente y energía</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>6.9. Uso de la escala de intensidad para describir los efectos de un sismo en las personas, las construcciones y el terreno.</t>
+          <t>6.19. Indagación del concepto de sostenibilidad y de las prácticas que la promueven.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Asigna una intensidad a la descripción de un sismo histórico de El Salvador según sus efectos y la distingue de la magnitud, que mide la energía liberada.</t>
+          <t>Explica qué es la sostenibilidad y propone tres prácticas para su escuela o comunidad, con el recurso que protege cada una.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad, Sismos y fallas geológicas, Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Ondas mecánicas transversales y longitudinales (8.°) de Ondas sísmicas, magnitud e intensidad (5.°), brecha 3, confianza alta</t>
+          <t>fusión: ambos temas trabajan Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>La magnitud depende de las ondas, que llegan en 8.°. En 5.° el tema se centra en la intensidad, que es observable. La magnitud y las ondas sísmicas quedan en 9.° (G09 5.8 y 5.9).</t>
+          <t>El concepto y sus prácticas se enseñan en dos temas seguidos. Unidos ganan sentido aplicado. Libera el tema de la acción 5.</t>
         </is>
       </c>
     </row>
@@ -1173,46 +1173,100 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G07-CIE-U5-5.15</t>
+          <t>G05-CIE-U6-6.6</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5. Recurso hídrico</t>
+          <t>6. Ciencias de la Tierra.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5.15. Construcción y uso de instrumentos para medir parámetros meteorológicos y comparación con el equipo de las estaciones del país.</t>
+          <t>6.6. Modelación de la deriva continental y de las corrientes de convección del manto que la impulsan.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Construye un pluviómetro o un anemómetro, lo calibra con datos de una estación oficial y explica qué mide cada instrumento de una estación meteorológica.</t>
+          <t>Reproduce con agua o aceite caliente y piezas flotantes cómo la convección mueve las placas y lo relaciona con la deriva de los continentes.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Deriva continental y expansión del fondo oceánico, Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>T8_27-E5.1 Equipo usado en investigaciones de ciencias de la Tierra (reforzar: 0 temas, sin cobertura)</t>
+          <t>prerrequisito: Convección del manto y energía interna de la Tierra (primer grado SV: nunca) de Tectónica de placas (5.°), confianza alta</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>El objetivo E5.1 aparece sin cobertura aunque el tema ya construye instrumentos. Se reformula para que el uso del equipo profesional de ciencias de la Tierra sea explícito y evaluable.</t>
+          <t>La tectónica de placas (6.7 y 6.8) se enseña sin explicar qué mueve las placas. Se reformula el tema anterior para introducir la convección del manto sin gastar presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>G05-CIE-U6-6.9</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>6. Ciencias de la Tierra.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>6.9. Uso de la escala de intensidad para describir los efectos de un sismo en las personas, las construcciones y el terreno.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Asigna una intensidad a la descripción de un sismo histórico de El Salvador según sus efectos y la distingue de la magnitud, que mide la energía liberada.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Ondas sísmicas, magnitud e intensidad, Sismos y fallas geológicas, Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>prerrequisito: Ondas mecánicas transversales y longitudinales (8.°) de Ondas sísmicas, magnitud e intensidad (5.°), brecha 3, confianza alta</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>La magnitud depende de las ondas, que llegan en 8.°. En 5.° el tema se centra en la intensidad, que es observable. La magnitud y las ondas sísmicas quedan en 9.° (G09 5.8 y 5.9).</t>
         </is>
       </c>
     </row>
@@ -1275,10 +1329,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1301,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1321,7 +1375,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>26</v>

--- a/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G05-G08.xlsx
+++ b/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Gravedad y órbitas (primer grado SV: nunca) de Formación del sistema solar (5.°), confianza alta; prerrequisito: Gravedad y órbitas, bloqueo de Mareas (CO 4, UY 5; primer grado SV: nunca)</t>
+          <t>prerrequisito: Gravedad y órbitas (primer grado SV: nunca) de Formación del sistema solar (5.°), confianza alta; T8_27-E4.1 Fenómenos observables por los movimientos de la Tierra y la Luna (reforzar: 0 temas); base de la acción 5</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Ningún tema antes de 10.° trabaja la gravedad como causa de las órbitas, y la necesitan la formación del sistema solar, la evolución estelar y las mareas. Se introduce de forma cualitativa. Se paga con la fusión 11.</t>
+          <t>Ningún tema antes de 10.° trabaja la gravedad como causa de las órbitas, y la necesitan la formación del sistema solar, la evolución estelar y la exploración espacial. Se introduce de forma cualitativa. Se paga con la fusión 11.</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>T8_27-E4.1 Fenómenos observables por los movimientos de la Tierra y la Luna (reforzar: 0 temas, sin cobertura); AU 6, CO 4.5, UY 5 (Mareas); prerrequisito: Gravedad y órbitas (acción 1)</t>
+          <t>T8_27-E4.1 Fenómenos observables por los movimientos de la Tierra y la Luna (reforzar: 0 temas, sin cobertura); prerrequisito: Gravedad y órbitas (acción 1)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>El objetivo E4.1 no tiene temas en el ciclo, y las mareas llegan en 9.°; Australia las enseña en 6.°, y Colombia y Uruguay antes. Va después de la gravedad. Se paga con la fusión 12.</t>
+          <t>El objetivo E4.1 no tiene temas en el ciclo. Se cubre en 6.°, después de la gravedad. Con Japón, las mareas dejan de ser candidato a adelantarse; el tema se justifica por el objetivo del marco. Se paga con la fusión 12.</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ENG 2, AU 3, UY 3, SG 5 (Ciclo del agua); sin bloqueos; T8_27-E2.2 El ciclo del agua; prerrequisito: cambios de estado del agua (G02 1.8)</t>
+          <t>ENG 2, AU 3, JP 3, UY 3, SG 5 (Ciclo del agua); sin bloqueos; T8_27-E2.2 El ciclo del agua; prerrequisito: cambios de estado del agua (G02 1.8)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Cuatro países, tres de alto desempeño, lo enseñan entre 2.° y 5.°; El Salvador, en 7.°. Sin bloqueos, pasa a 5.° antes del suelo y la erosión. El ciclo urbano sigue en 7.° (5.2).</t>
+          <t>Cinco países, los cuatro de alto desempeño, lo enseñan entre 2.° y 5.°; El Salvador, en 7.°. Sin bloqueos, pasa a 5.° antes del suelo y la erosión. El ciclo urbano sigue en 7.° (5.2).</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>AU 2, ENG 2, CO 8.5 (Tiempo atmosférico y sus variables); prerrequisito: Temperatura y escalas termométricas (6.°), bloqueo: impide llegar a 5.°; T8_27-E5.1 Equipo usado en investigaciones de ciencias de la Tierra (reforzar: 0 temas, sin cobertura)</t>
+          <t>AU 2, ENG 2, JP 3, CO 8.5 (Tiempo atmosférico y sus variables); prerrequisito: Temperatura y escalas termométricas (6.°), bloqueo: impide llegar a 5.°; T8_27-E5.1 Equipo usado en investigaciones de ciencias de la Tierra (reforzar: 0 temas, sin cobertura)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Inglaterra y Australia trabajan el tiempo atmosférico desde 2.°. Su bloqueo, la temperatura, está en 6.°, así que va a 6.° y no a 5.°. Se reformula para cubrir el objetivo E5.1.</t>
+          <t>Inglaterra, Australia y Japón trabajan el tiempo atmosférico entre 2.° y 3.°. Su bloqueo, la temperatura, está en 6.°, así que va a 6.° y no a 5.°. Se reformula para cubrir el objetivo E5.1.</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Tiempo atmosférico y sus variables (también 5.15 y 5.18); AU 2, ENG 2, CO 8.5 (Tiempo atmosférico y sus variables); prerrequisito: Temperatura y escalas termométricas (6.°)</t>
+          <t>fusión: ambos temas trabajan Tiempo atmosférico y sus variables (también 5.15 y 5.18); AU 2, ENG 2, JP 3, CO 8.5 (Tiempo atmosférico y sus variables); prerrequisito: Temperatura y escalas termométricas (6.°)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1168,51 +1168,45 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>G05-CIE-U6-6.6</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6. Ciencias de la Tierra.</t>
+          <t>6. Ambiente y energía (después de 6.6 y antes de 6.13)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6.6. Modelación de la deriva continental y de las corrientes de convección del manto que la impulsan.</t>
+          <t>6.21. Modelación del ciclo del carbono entre la atmósfera, la biosfera, la hidrosfera y la geosfera.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Reproduce con agua o aceite caliente y piezas flotantes cómo la convección mueve las placas y lo relaciona con la deriva de los continentes.</t>
+          <t>Representa en un diagrama de flujos cómo la fotosíntesis, la respiración, la combustión y los océanos mueven el carbono entre los sistemas de la Tierra e identifica qué flujo aumentan las actividades humanas.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico, Convección del manto y energía interna de la Tierra</t>
+          <t>Ciclo del carbono en los sistemas terrestres, Sistemas terrestres y sus interacciones, Combustión, Fotosíntesis</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Convección del manto y energía interna de la Tierra (primer grado SV: nunca) de Tectónica de placas (5.°), confianza alta</t>
+          <t>ENG 6, JP 5, AU 8, CO 6.5 (Ciclo del carbono en los sistemas terrestres); hoy se introduce en 10.°; prerrequisito: Fotosíntesis (6.°) y Combustión (7.°, G07 6.5), bloqueos que impiden llegar a 6.°; prerrequisito: Sistemas terrestres y sus interacciones (primer grado SV: nunca), se introduce en el mismo tema</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>La tectónica de placas (6.7 y 6.8) se enseña sin explicar qué mueve las placas. Se reformula el tema anterior para introducir la convección del manto sin gastar presupuesto.</t>
+          <t>Tres países de alto desempeño lo enseñan entre 5.° y 8.°; El Salvador, en 10.°. Va en 7.°, tras la combustión, y antes del efecto invernadero y el cambio climático, que lo necesitan. Se paga con la fusión 14.</t>
         </is>
       </c>
     </row>
@@ -1222,49 +1216,211 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>G07-CIE-U6-6.14, G07-CIE-U6-6.15</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>6. Ambiente y energía (después de 6.13)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>6.14. Análisis de las causas antropogénicas y de los efectos del cambio climático.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Relaciona en un esquema causa-efecto tres actividades humanas con el aumento de gases de efecto invernadero y tres efectos del cambio climático en El Salvador.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Cambio climático: causas y efectos, Calentamiento global</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Cambio climático: causas y efectos; prerrequisito: Ciclo del carbono en los sistemas terrestres (acción 13)</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Causas y efectos del cambio climático se enseñan en dos temas seguidos. Unidos, y precedidos por el ciclo del carbono, ganan una explicación completa. Libera el tema de la acción 13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>G07-CIE-U5-5.12, G07-CIE-U5-5.13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6. Ambiente y energía (después de 6.21 y antes de 6.13)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6.22. Reconocimiento de los principales contaminantes y parámetros que inciden en la calidad del aire. | 6.23. Clasificación de la calidad del aire de acuerdo con el Índice Centroamericano de Calidad del Aire (ICCA).</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Identifica los contaminantes que produce la quema de combustibles y explica cómo afectan la calidad del aire de su comunidad. | Clasifica datos reales de una estación de monitoreo según el ICCA y propone una medida de protección para cada categoría.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Calidad del aire y contaminación atmosférica, Composición del aire y contaminantes atmosféricos, Combustibles fósiles: formación y uso</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>CO 4.5, UY 5, JP 5, SG 5 (Calidad del aire y contaminación atmosférica); prerrequisito: Combustibles fósiles: formación y uso (7.°, G07 6.4), bloqueo: impide llegar a 5.° y hoy se enseña después, en la unidad 6</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Japón y Singapur la enseñan en 5.°, pero su bloqueo, los combustibles fósiles, está en 7.°. No puede adelantarse de grado; se reubica dentro de 7.° después de los combustibles y la combustión, junto al efecto invernadero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>G05-CIE-U6-6.6</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>6. Ciencias de la Tierra.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>6.6. Modelación de la deriva continental y de las corrientes de convección del manto que la impulsan.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Reproduce con agua o aceite caliente y piezas flotantes cómo la convección mueve las placas y lo relaciona con la deriva de los continentes.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Deriva continental y expansión del fondo oceánico, Convección del manto y energía interna de la Tierra</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>prerrequisito: Convección del manto y energía interna de la Tierra (primer grado SV: nunca) de Tectónica de placas (5.°), confianza alta</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>La tectónica de placas (6.7 y 6.8) se enseña sin explicar qué mueve las placas. Se reformula el tema anterior para introducir la convección del manto sin gastar presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>G05-CIE-U6-6.9</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>6. Ciencias de la Tierra.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>6.9. Uso de la escala de intensidad para describir los efectos de un sismo en las personas, las construcciones y el terreno.</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Asigna una intensidad a la descripción de un sismo histórico de El Salvador según sus efectos y la distingue de la magnitud, que mide la energía liberada.</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Ondas sísmicas, magnitud e intensidad, Sismos y fallas geológicas, Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>prerrequisito: Ondas mecánicas transversales y longitudinales (8.°) de Ondas sísmicas, magnitud e intensidad (5.°), brecha 3, confianza alta</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>La magnitud depende de las ondas, que llegan en 8.°. En 5.° el tema se centra en la intensidad, que es observable. La magnitud y las ondas sísmicas quedan en 9.° (G09 5.8 y 5.9).</t>
         </is>

--- a/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G05-G08.xlsx
+++ b/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G05-G08.xlsx
@@ -1412,17 +1412,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad, Sismos y fallas geológicas, Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>Sismos y fallas geológicas, Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Ondas mecánicas transversales y longitudinales (8.°) de Ondas sísmicas, magnitud e intensidad (5.°), brecha 3, confianza alta</t>
+          <t>prerrequisito: Ondas mecánicas transversales y longitudinales (8.°) de Ondas sísmicas, magnitud e intensidad (5.°), brecha 3, confianza alta; v4: la etiqueta «Ondas sísmicas, magnitud e intensidad» se retira de 6.9 (quitar_conceptos): el tema reformulado trabaja la intensidad observable, no las ondas; el concepto se introduce en 9.° (G09 5.8 y 5.9)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>La magnitud depende de las ondas, que llegan en 8.°. En 5.° el tema se centra en la intensidad, que es observable. La magnitud y las ondas sísmicas quedan en 9.° (G09 5.8 y 5.9).</t>
+          <t>La magnitud depende de las ondas, que llegan en 8.°. En 5.° el tema se centra en la intensidad, que es observable. La magnitud y las ondas sísmicas quedan en 9.° (G09 5.8 y 5.9). Por eso el tema deja de llevar la etiqueta de ondas sísmicas, que fijaba su primer grado en 5.°.</t>
         </is>
       </c>
     </row>
